--- a/script_migration_stock_config/static/data/Purchase Return Create (stock.location).xlsx
+++ b/script_migration_stock_config/static/data/Purchase Return Create (stock.location).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/waiyan/Project/Odoo/ppg/ppg/ppg/ppg/script_migration_stock_config/static/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A5AFC5-76A9-CD46-AB74-8DED7273B07A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91885330-379D-5A43-8045-69B24EB7AE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="660" windowWidth="30160" windowHeight="17900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="89">
   <si>
     <t>Location Name</t>
   </si>
@@ -43,9 +43,6 @@
     <t>Inventory Loss</t>
   </si>
   <si>
-    <t xml:space="preserve">Goods Received not Purchased </t>
-  </si>
-  <si>
     <t>စော်ဘွားကြီးကုန်း Showroom (23.11.20)</t>
   </si>
   <si>
@@ -289,7 +286,7 @@
     <t>Loss Account</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>Goods Received not Purchased</t>
   </si>
 </sst>
 </file>
@@ -663,7 +660,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -677,10 +674,10 @@
         <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -694,10 +691,10 @@
         <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -711,10 +708,10 @@
         <v>6</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -728,10 +725,10 @@
         <v>6</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -745,10 +742,10 @@
         <v>6</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -762,10 +759,10 @@
         <v>6</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -779,10 +776,10 @@
         <v>6</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -796,10 +793,10 @@
         <v>6</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -813,10 +810,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -830,10 +827,10 @@
         <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -847,10 +844,10 @@
         <v>6</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -864,10 +861,10 @@
         <v>6</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -881,10 +878,10 @@
         <v>6</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -898,10 +895,10 @@
         <v>6</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -915,10 +912,10 @@
         <v>6</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -932,10 +929,10 @@
         <v>6</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -949,10 +946,10 @@
         <v>6</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -966,10 +963,10 @@
         <v>6</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -983,10 +980,10 @@
         <v>6</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1000,10 +997,10 @@
         <v>6</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1017,10 +1014,10 @@
         <v>6</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1034,10 +1031,10 @@
         <v>6</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1051,10 +1048,10 @@
         <v>6</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1068,10 +1065,10 @@
         <v>6</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1085,10 +1082,10 @@
         <v>6</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1102,10 +1099,10 @@
         <v>6</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1119,10 +1116,10 @@
         <v>6</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1136,10 +1133,10 @@
         <v>6</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1153,10 +1150,10 @@
         <v>6</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1170,10 +1167,10 @@
         <v>6</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1187,10 +1184,10 @@
         <v>6</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1204,10 +1201,10 @@
         <v>6</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1221,10 +1218,10 @@
         <v>6</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1238,10 +1235,10 @@
         <v>6</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1255,10 +1252,10 @@
         <v>6</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1272,10 +1269,10 @@
         <v>6</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1289,10 +1286,10 @@
         <v>6</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1306,10 +1303,10 @@
         <v>6</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1323,10 +1320,10 @@
         <v>6</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1340,10 +1337,10 @@
         <v>6</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1357,10 +1354,10 @@
         <v>6</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1374,10 +1371,10 @@
         <v>6</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1391,10 +1388,10 @@
         <v>6</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1408,10 +1405,10 @@
         <v>6</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1425,10 +1422,10 @@
         <v>6</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1442,10 +1439,10 @@
         <v>6</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1459,10 +1456,10 @@
         <v>6</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1476,10 +1473,10 @@
         <v>6</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1493,10 +1490,10 @@
         <v>6</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1510,10 +1507,10 @@
         <v>6</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1527,10 +1524,10 @@
         <v>6</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1544,10 +1541,10 @@
         <v>6</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1561,10 +1558,10 @@
         <v>6</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1578,10 +1575,10 @@
         <v>6</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1595,10 +1592,10 @@
         <v>6</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1612,10 +1609,10 @@
         <v>6</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1629,10 +1626,10 @@
         <v>6</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1646,10 +1643,10 @@
         <v>6</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1663,10 +1660,10 @@
         <v>6</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1680,10 +1677,10 @@
         <v>6</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1697,10 +1694,10 @@
         <v>6</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1714,10 +1711,10 @@
         <v>6</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1731,10 +1728,10 @@
         <v>6</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1748,10 +1745,10 @@
         <v>6</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1765,10 +1762,10 @@
         <v>6</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1782,10 +1779,10 @@
         <v>6</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1799,10 +1796,10 @@
         <v>6</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1816,10 +1813,10 @@
         <v>6</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1833,10 +1830,10 @@
         <v>6</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1850,10 +1847,10 @@
         <v>6</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1867,10 +1864,10 @@
         <v>6</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1884,10 +1881,10 @@
         <v>6</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1901,10 +1898,10 @@
         <v>6</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1918,10 +1915,10 @@
         <v>6</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1935,10 +1932,10 @@
         <v>6</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1952,10 +1949,10 @@
         <v>6</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1969,10 +1966,10 @@
         <v>6</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1986,10 +1983,10 @@
         <v>6</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2003,10 +2000,10 @@
         <v>6</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -2020,10 +2017,10 @@
         <v>6</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/script_migration_stock_config/static/data/Purchase Return Create (stock.location).xlsx
+++ b/script_migration_stock_config/static/data/Purchase Return Create (stock.location).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/waiyan/Project/Odoo/ppg/ppg/ppg/ppg/script_migration_stock_config/static/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91885330-379D-5A43-8045-69B24EB7AE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C033F4CD-E0DB-EE4C-B6C8-4190FB65B926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="80" yWindow="660" windowWidth="30160" windowHeight="17900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="90">
   <si>
     <t>Location Name</t>
   </si>
@@ -287,13 +287,16 @@
   </si>
   <si>
     <t>Goods Received not Purchased</t>
+  </si>
+  <si>
+    <t>ပခုက္ကူ Showroom (1.10.21)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -308,6 +311,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF111827"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -330,12 +339,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -640,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="30.6640625" customWidth="1"/>
@@ -2023,6 +2033,23 @@
         <v>88</v>
       </c>
     </row>
+    <row r="82" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+      <c r="A82" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
